--- a/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,6 +767,141 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>38637</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lid - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>49.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>35130</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Foil Roll - 18"</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>26.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Container - Deli (8oz)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>31.75</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>63.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15509</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>59.94</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>119.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22435</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Container - Deli (16oz)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>35.88</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>71.76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
